--- a/spreadsheets/BestBuy.xlsx
+++ b/spreadsheets/BestBuy.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BestBuy Surface Catalog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BestBuy Surface Catalog'!$A$1:$U$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BestBuy Surface Catalog'!$A$1:$V$14</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -32,7 +31,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -49,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,17 +62,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -93,7 +93,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -456,8 +456,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.75"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -472,17 +472,15 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="14" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="17" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="20" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="29" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Retailer</t>
@@ -584,6 +582,11 @@
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>PreOrders</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
@@ -617,7 +620,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -635,12 +638,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -678,7 +681,10 @@
       <c r="T2" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -712,7 +718,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -730,12 +736,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -773,7 +779,10 @@
       <c r="T3" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -807,7 +816,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
@@ -825,12 +834,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -868,7 +877,10 @@
       <c r="T4" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -902,7 +914,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
@@ -920,12 +932,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -963,7 +975,10 @@
       <c r="T5" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -997,7 +1012,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -1015,12 +1030,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1058,7 +1073,10 @@
       <c r="T6" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1092,7 +1110,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
@@ -1110,12 +1128,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1153,7 +1171,10 @@
       <c r="T7" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1187,7 +1208,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -1205,12 +1226,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1248,7 +1269,10 @@
       <c r="T8" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U8" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1282,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
@@ -1300,12 +1324,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1343,7 +1367,10 @@
       <c r="T9" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U9" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1377,7 +1404,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Snapdragon X Elite (12-core)</t>
+          <t>20-core NVIDIA Grace ARM (TSMC 3nm, w/ MediaTek)</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
@@ -1395,12 +1422,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Integrated Qualcomm Adreno + NPU (45 TOPS)</t>
+          <t>Blackwell RTX (up to 6,144 CUDA cores, 5th-gen Tensor)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45 TOPS (NPU)</t>
+          <t>Up to 1 PFLOP FP4 (sparsity)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1438,7 +1465,10 @@
       <c r="T10" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U10" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1533,7 +1563,10 @@
       <c r="T11" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U11" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1628,7 +1661,10 @@
       <c r="T12" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1723,7 +1759,10 @@
       <c r="T13" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="U13" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
@@ -1818,14 +1857,17 @@
       <c r="T14" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="U14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>1-Year Limited</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U14"/>
+  <autoFilter ref="A1:V14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>